--- a/tickets-template.xlsx
+++ b/tickets-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,17 +52,8 @@
       <color rgb="00E8304B"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft JhengHei"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Microsoft JhengHei"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF0EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,12 +122,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,34 +139,31 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,24 +531,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="72" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>★ 使用說明：同一個景點的不同平台，attraction 欄位請填完全一樣的名稱，網站才會把它們合併成一張卡片。  type 限填：交通運輸 / 景點門票 / 一日遊 / 體驗活動  subtype 限填：遊樂園 / 博物館 / 水族館 / 展覽 / 自然景觀 / 台鐵 / 高鐵 / 新幹線 / 阪急 / JR Pass / 地鐵 / 機場接送 / 近郊一日遊 / 城市導覽 / 包車 / 料理體驗 / 文化體驗 / 戶外活動 / 溫泉</t>
+          <t>★ 使用說明：
+① attraction：同景點不同平台填相同名稱 → 網站自動合併成一張卡片
+② url_scrape：平台官方原始網址（給 Claude 更新價格用）
+③ url_affiliate：你的聯盟行銷轉址連結（使用者點「立即預訂」按鈕用）。若還沒有聯盟連結，填與 url_scrape 相同即可
+④ type 限填：交通運輸 / 景點門票 / 一日遊 / 體驗活動</t>
         </is>
       </c>
     </row>
@@ -563,7 +561,7 @@
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>景點 / 票券主標題
-（同景點填相同名稱→合併卡片）</t>
+（同景點填相同→合併卡片）</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -589,14 +587,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>票券類別
-交通運輸/景點門票/一日遊/體驗活動</t>
+          <t>票券類別</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>細項
-（見說明列）</t>
+（見「允許值說明」工作表）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -607,8 +604,14 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>購票連結
-（可直接貼官網 URL）</t>
+          <t>官方原始網址
+（Claude 爬價格用）</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>聯盟行銷連結
+（使用者點按鈕用）</t>
         </is>
       </c>
     </row>
@@ -638,7 +641,7 @@
           <t>台北</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -648,10 +651,15 @@
           <t>展覽</t>
         </is>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="6" t="n">
         <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/1659-taipei-101-taipei/</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/1659-taipei-101-taipei/</t>
         </is>
@@ -683,7 +691,7 @@
           <t>台北</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -693,10 +701,15 @@
           <t>博物館</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="11" t="n">
         <v>120</v>
       </c>
       <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/101875</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/101875</t>
         </is>
@@ -728,7 +741,7 @@
           <t>台北</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>一日遊</t>
         </is>
@@ -738,10 +751,15 @@
           <t>近郊一日遊</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="11" t="n">
         <v>3200</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/11679</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/11679</t>
         </is>
@@ -773,7 +791,7 @@
           <t>高雄</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>一日遊</t>
         </is>
@@ -783,10 +801,15 @@
           <t>包車</t>
         </is>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/142529</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/142529</t>
         </is>
@@ -818,7 +841,7 @@
           <t>全台</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>交通運輸</t>
         </is>
@@ -828,10 +851,15 @@
           <t>高鐵</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="11" t="n">
         <v>1500</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/2700</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/2700</t>
         </is>
@@ -863,7 +891,7 @@
           <t>東京</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -873,10 +901,15 @@
           <t>遊樂園</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="6" t="n">
         <v>2600</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/695-tokyo-disney-resort-1-day-pass-tokyo/</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/695-tokyo-disney-resort-1-day-pass-tokyo/</t>
         </is>
@@ -908,7 +941,7 @@
           <t>東京</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -918,10 +951,15 @@
           <t>遊樂園</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="11" t="n">
         <v>2600</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/19252-tokyo-disney-resort-disneyland-disneysea</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/19252-tokyo-disney-resort-disneyland-disneysea</t>
         </is>
@@ -953,7 +991,7 @@
           <t>東京</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -963,10 +1001,15 @@
           <t>展覽</t>
         </is>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="6" t="n">
         <v>680</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/41352-tokyo-skytree/</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/41352-tokyo-skytree/</t>
         </is>
@@ -998,7 +1041,7 @@
           <t>東京</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -1008,10 +1051,15 @@
           <t>展覽</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="11" t="n">
         <v>1050</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/22396-japan-teamlab-planets-tokyo-ticket</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/22396-japan-teamlab-planets-tokyo-ticket</t>
         </is>
@@ -1043,7 +1091,7 @@
           <t>大阪</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -1053,10 +1101,15 @@
           <t>遊樂園</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>1950</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/46604-universal-studios-japan-e-ticket-osaka-qr-code-direct-entry/</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/46604-universal-studios-japan-e-ticket-osaka-qr-code-direct-entry/</t>
         </is>
@@ -1088,7 +1141,7 @@
           <t>大阪</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>交通運輸</t>
         </is>
@@ -1098,10 +1151,15 @@
           <t>地鐵</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>1050</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/82312-amazing-pass-osaka/</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/82312-amazing-pass-osaka/</t>
         </is>
@@ -1133,7 +1191,7 @@
           <t>京都</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>一日遊</t>
         </is>
@@ -1143,10 +1201,15 @@
           <t>近郊一日遊</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="11" t="n">
         <v>2800</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/39456</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/39456</t>
         </is>
@@ -1178,7 +1241,7 @@
           <t>京都</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>體驗活動</t>
         </is>
@@ -1188,10 +1251,15 @@
           <t>文化體驗</t>
         </is>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="11" t="n">
         <v>1200</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/36881</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/36881</t>
         </is>
@@ -1223,7 +1291,7 @@
           <t>箱根</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>交通運輸</t>
         </is>
@@ -1233,10 +1301,15 @@
           <t>新幹線</t>
         </is>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="11" t="n">
         <v>2100</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/133992-fuji-hakone-3-day-travel-pass-tokyo</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/133992-fuji-hakone-3-day-travel-pass-tokyo</t>
         </is>
@@ -1268,7 +1341,7 @@
           <t>富士山</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>景點門票</t>
         </is>
@@ -1278,10 +1351,15 @@
           <t>遊樂園</t>
         </is>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="11" t="n">
         <v>1680</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kkday.com/zh-tw/product/104303</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>https://www.kkday.com/zh-tw/product/104303</t>
         </is>
@@ -1313,7 +1391,7 @@
           <t>全國</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>交通運輸</t>
         </is>
@@ -1323,10 +1401,15 @@
           <t>JR Pass</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>15800</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.klook.com/zh-TW/activity/1420-7-day-whole-japan-rail-pass-jr-pass/</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>https://www.klook.com/zh-TW/activity/1420-7-day-whole-japan-rail-pass-jr-pass/</t>
         </is>
@@ -1334,7 +1417,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1346,68 +1429,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>欄位</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>允許值（只能填這些，否則網站篩選器會對不上）</t>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>允許值 / 說明（只能填這些，否則篩選器對不上）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Klook　　KKday</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>台灣　日本　韓國　泰國　（其他國家可自行新增）</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>交通運輸　景點門票　一日遊　體驗活動</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>subtype</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>【交通運輸】台鐵 / 高鐵 / 新幹線 / 阪急 / JR Pass / 地鐵 / 機場接送
 【景點門票】遊樂園 / 博物館 / 水族館 / 展覽 / 自然景觀
@@ -1416,6 +1499,30 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>url_scrape</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>平台官方原始商品頁網址，不用轉址，直接貼原始 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>url_affiliate</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>你的聯盟行銷轉址連結。若還沒有，填與 url_scrape 相同即可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tickets-template.xlsx
+++ b/tickets-template.xlsx
@@ -49,7 +49,7 @@
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
-      <color rgb="00E8304B"/>
+      <color rgb="0000AADC"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -82,7 +82,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE8EB"/>
+        <fgColor rgb="00E3F6FC"/>
       </patternFill>
     </fill>
     <fill>
